--- a/FigafIRTinfrastructure/IntegrationFlow/LatencyTest/Documentation.xlsx
+++ b/FigafIRTinfrastructure/IntegrationFlow/LatencyTest/Documentation.xlsx
@@ -260,7 +260,7 @@
     <t>SAP_ProfileId</t>
   </si>
   <si>
-    <t>sampledev(cpi-trial-alex)-&gt;sampleqa(cpi-trial-alex)</t>
+    <t>sampledev(trial-cpi-alex)-&gt;sampleqa(trial-cpi-alex)</t>
   </si>
   <si>
     <t>sampledev</t>
